--- a/artfynd/A 14293-2022 artfynd.xlsx
+++ b/artfynd/A 14293-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14293-2022 artfynd.xlsx
+++ b/artfynd/A 14293-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103968853</v>
+        <v>103968933</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550727.0759549271</v>
+        <v>550752</v>
       </c>
       <c r="R2" t="n">
-        <v>7090759.080070975</v>
+        <v>7090774</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,11 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -801,37 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103968897</v>
+        <v>103968898</v>
       </c>
       <c r="B3" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550727.8566142559</v>
+        <v>550734</v>
       </c>
       <c r="R3" t="n">
-        <v>7090765.250276772</v>
+        <v>7090756</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,32 +907,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103968835</v>
+        <v>103968853</v>
       </c>
       <c r="B4" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -962,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550739.0420426592</v>
+        <v>550727</v>
       </c>
       <c r="R4" t="n">
-        <v>7090754.436209769</v>
+        <v>7090759</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,6 +998,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1043,15 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103968898</v>
+        <v>103968843</v>
       </c>
       <c r="B5" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550734.1704016965</v>
+        <v>550735</v>
       </c>
       <c r="R5" t="n">
-        <v>7090756.116436822</v>
+        <v>7090767</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,15 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103968933</v>
+        <v>103968912</v>
       </c>
       <c r="B6" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1204,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550751.9292141238</v>
+        <v>550739</v>
       </c>
       <c r="R6" t="n">
-        <v>7090774.437495881</v>
+        <v>7090757</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1249,7 +1224,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,37 +1260,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103968912</v>
+        <v>103968835</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1325,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550738.9992182024</v>
+        <v>550739</v>
       </c>
       <c r="R7" t="n">
-        <v>7090757.074464774</v>
+        <v>7090754</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,37 +1376,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103968843</v>
+        <v>103968897</v>
       </c>
       <c r="B8" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1446,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550734.8725427187</v>
+        <v>550728</v>
       </c>
       <c r="R8" t="n">
-        <v>7090767.123437493</v>
+        <v>7090765</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 14293-2022 artfynd.xlsx
+++ b/artfynd/A 14293-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103968933</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103968898</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103968853</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1141,6 +1161,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103968843</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103968912</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1373,6 +1403,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103968835</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1489,8 +1524,22 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103968897</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>